--- a/data/stx_xlsx/COREa.ST.xlsx
+++ b/data/stx_xlsx/COREa.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="415">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>LT Debt</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Leasing liabilities</t>
@@ -1386,7 +1389,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1470,6 +1473,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -12472,8 +12478,8 @@
       <c r="X77" s="17"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="14" t="s">
-        <v>227</v>
+      <c r="A78" s="28" t="s">
+        <v>238</v>
       </c>
       <c r="B78" s="17">
         <v>19140.04</v>
@@ -12515,7 +12521,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B79" s="15">
         <v>1645.67</v>
@@ -12557,7 +12563,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B80" s="15">
         <v>5351.43</v>
@@ -12669,7 +12675,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B82" s="16">
         <v>29.52</v>
@@ -12733,7 +12739,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
@@ -12773,7 +12779,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -12803,7 +12809,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="21">
         <v>26254.14</v>
@@ -12875,7 +12881,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="21">
         <v>40061.34</v>
@@ -12949,7 +12955,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B87" s="17"/>
       <c r="C87" s="15">
@@ -13019,7 +13025,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="17">
@@ -13081,7 +13087,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="15">
@@ -13143,7 +13149,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B90" s="17"/>
       <c r="C90" s="23">
@@ -13213,7 +13219,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B91" s="17"/>
       <c r="C91" s="15">
@@ -13243,7 +13249,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -13279,7 +13285,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
@@ -13315,7 +13321,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -13347,7 +13353,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B95" s="21">
         <v>18031.27</v>
@@ -13421,7 +13427,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B96" s="17">
         <v>0.0</v>
@@ -13459,7 +13465,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B97" s="21"/>
       <c r="C97" s="21">
@@ -13495,7 +13501,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B98" s="21">
         <v>18031.27</v>
@@ -13569,7 +13575,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B99" s="21">
         <v>58092.6</v>
@@ -13643,7 +13649,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B100" s="15">
         <v>1383.87</v>
@@ -13717,7 +13723,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B101" s="15">
         <v>1423.07</v>
@@ -13791,7 +13797,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B102" s="16">
         <v>39.21</v>
@@ -13865,7 +13871,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B103" s="16">
         <v>11.7</v>
@@ -13915,7 +13921,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -13975,7 +13981,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
@@ -14021,7 +14027,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -14067,7 +14073,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
@@ -14113,7 +14119,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -14159,7 +14165,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
@@ -14205,7 +14211,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
@@ -14255,7 +14261,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B111" s="17"/>
       <c r="C111" s="15">
@@ -14319,7 +14325,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B112" s="17"/>
       <c r="C112" s="15">
@@ -14381,7 +14387,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B113" s="17"/>
       <c r="C113" s="15">
@@ -14443,7 +14449,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B114" s="17"/>
       <c r="C114" s="15">
@@ -14503,7 +14509,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B115" s="17"/>
       <c r="C115" s="15">
@@ -14563,7 +14569,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B116" s="17"/>
       <c r="C116" s="15">
@@ -14595,7 +14601,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B117" s="17"/>
       <c r="C117" s="15">
@@ -14639,7 +14645,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -14673,7 +14679,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B119" s="17"/>
       <c r="C119" s="15">
@@ -14711,7 +14717,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B120" s="17"/>
       <c r="C120" s="15">
@@ -14749,7 +14755,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B121" s="17"/>
       <c r="C121" s="15">
@@ -14787,7 +14793,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -14817,7 +14823,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B123" s="16">
         <v>93.12</v>
@@ -14891,7 +14897,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B124" s="16">
         <v>2.91</v>
@@ -14965,7 +14971,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B125" s="16">
         <v>90.21</v>
@@ -15039,7 +15045,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B126" s="16">
         <v>0.07</v>
@@ -15113,7 +15119,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B127" s="16">
         <v>12.42</v>
@@ -15173,7 +15179,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B128" s="17">
         <v>0.0</v>
@@ -15233,7 +15239,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B129" s="16">
         <v>12.41</v>
@@ -15293,7 +15299,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B130" s="15">
         <v>1322.4</v>
@@ -15339,7 +15345,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B131" s="16">
         <v>36.25</v>
@@ -15385,7 +15391,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B132" s="15">
         <v>1286.15</v>
@@ -15431,7 +15437,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B133" s="16">
         <v>0.93</v>
@@ -15477,7 +15483,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B134" s="16">
         <v>7.55</v>
@@ -15515,7 +15521,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B135" s="16">
         <v>7.5</v>
@@ -15553,7 +15559,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B136" s="16">
         <v>0.04</v>
@@ -15591,7 +15597,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B137" s="16">
         <v>0.01</v>
@@ -16511,7 +16517,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16910,73 +16916,73 @@
         <v>45</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -17055,7 +17061,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -17157,7 +17163,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B20" s="15">
         <v>1009.38</v>
@@ -17263,7 +17269,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B22" s="23">
         <v>-145.11</v>
@@ -17315,7 +17321,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B23" s="16">
         <v>19.06</v>
@@ -17367,7 +17373,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B24" s="16">
         <v>7.41</v>
@@ -17419,7 +17425,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B25" s="23">
         <v>-1140.72</v>
@@ -17471,7 +17477,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B26" s="22">
         <v>-1.06</v>
@@ -17545,7 +17551,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B27" s="22">
         <v>-86.85</v>
@@ -17587,7 +17593,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B28" s="23">
         <v>-157.82</v>
@@ -17661,7 +17667,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B29" s="16">
         <v>8.47</v>
@@ -17715,7 +17721,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -17747,7 +17753,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -17797,7 +17803,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -17839,7 +17845,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" s="17">
         <v>0.0</v>
@@ -17889,7 +17895,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -17929,7 +17935,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -17969,7 +17975,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -18017,7 +18023,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -18051,7 +18057,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -18085,7 +18091,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -18117,7 +18123,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -18157,7 +18163,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -18205,7 +18211,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -18245,7 +18251,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -18275,7 +18281,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -18311,7 +18317,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -18347,7 +18353,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -18379,7 +18385,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B47" s="19">
         <v>860.04</v>
@@ -18453,7 +18459,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B48" s="23">
         <v>-1585.57</v>
@@ -18507,7 +18513,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -18569,7 +18575,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B50" s="15">
         <v>5073.39</v>
@@ -18635,7 +18641,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" s="15">
         <v>461.79</v>
@@ -18675,7 +18681,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" s="17">
         <v>0.0</v>
@@ -18729,7 +18735,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -18765,7 +18771,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="17">
@@ -18799,7 +18805,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -18833,7 +18839,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -18867,7 +18873,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -18905,7 +18911,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -18963,7 +18969,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -18995,7 +19001,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="17">
@@ -19027,7 +19033,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B61" s="19">
         <v>3949.62</v>
@@ -19101,7 +19107,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B62" s="23">
         <v>-553.94</v>
@@ -19163,7 +19169,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -19193,7 +19199,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -19223,7 +19229,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B65" s="22">
         <v>-3.18</v>
@@ -19283,7 +19289,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B66" s="15">
         <v>979.73</v>
@@ -19323,7 +19329,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B67" s="17">
         <v>19730.08</v>
@@ -19387,7 +19393,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B68" s="26">
         <v>-22344.1</v>
@@ -19451,7 +19457,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B69" s="23">
         <v>-1296.42</v>
@@ -19527,7 +19533,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -19573,7 +19579,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -19623,7 +19629,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -19653,7 +19659,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -19685,7 +19691,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -19715,7 +19721,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B76" s="24">
         <v>-3487.82</v>
@@ -19789,7 +19795,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B77" s="15">
         <v>640.77</v>
@@ -19863,7 +19869,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B78" s="15">
         <v>1972.61</v>
@@ -19937,7 +19943,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B79" s="22">
         <v>-31.77</v>
@@ -19983,7 +19989,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B80" s="15">
         <v>1321.84</v>
@@ -20025,7 +20031,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B81" s="19">
         <v>1290.06</v>
@@ -20099,7 +20105,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -20131,7 +20137,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
@@ -21108,7 +21114,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21278,10 +21284,10 @@
         <v>40</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -21671,7 +21677,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -21769,2657 +21775,2657 @@
         <v>73</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>364</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="B21" s="32">
         <v>47127.07</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>50584.26</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>56985.67</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>88144.85</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>18811.16</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>16474.88</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>13963.16</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>12539.53</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>8403.06</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>7133.28</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>6751.75</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>5604.63</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>4645.47</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>4433.53</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>3351.79</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>2336.62</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>2820.24</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>1748.62</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>-4.29</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>-6.09</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="34">
         <v>-1.74</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="34">
         <v>-7.82</v>
       </c>
-      <c r="X21" s="33">
+      <c r="X21" s="34">
         <v>-4.48</v>
       </c>
-      <c r="Y21" s="34">
+      <c r="Y21" s="35">
         <v>0.16</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="B22" s="32">
         <v>54512.08</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>47689.01</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>37821.37</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>29792.85</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>14887.39</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>11268.28</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>9672.91</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>8245.17</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>6466.5</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>6351.19</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>5250.71</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>4379.4</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>3502.66</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>2969.5</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>2081.86</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>1315.1</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>931.37</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>345.99</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="34">
         <v>-5.07</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="34">
         <v>-3.9</v>
       </c>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="B24" s="32">
         <v>13594.7</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>15837.8</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>12688.79</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>41779.9</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>8579.04</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>10835.77</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>4932.56</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>4605.41</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>1269.81</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>1251.59</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>1401.39</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>1095.92</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>862.67</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>827.34</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>891.12</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>129.36</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>109.88</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>130.54</v>
       </c>
-      <c r="T24" s="34">
+      <c r="T24" s="35">
         <v>1.08</v>
       </c>
-      <c r="U24" s="34">
+      <c r="U24" s="35">
         <v>1.52</v>
       </c>
-      <c r="V24" s="34">
+      <c r="V24" s="35">
         <v>1.26</v>
       </c>
-      <c r="W24" s="34">
+      <c r="W24" s="35">
         <v>1.47</v>
       </c>
-      <c r="X24" s="34">
+      <c r="X24" s="35">
         <v>1.45</v>
       </c>
-      <c r="Y24" s="34">
+      <c r="Y24" s="35">
         <v>4.27</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="B25" s="32">
         <v>19232.37</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>18497.67</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>15284.28</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>14090.4</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>6425.61</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>4453.54</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>2664.88</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>1953.71</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>1169.77</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>1210.26</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>1076.05</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>812.58</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>560.14</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>419.83</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>254.55</v>
       </c>
-      <c r="Q25" s="34">
+      <c r="Q25" s="35">
         <v>71.47</v>
       </c>
-      <c r="R25" s="34">
+      <c r="R25" s="35">
         <v>50.36</v>
       </c>
-      <c r="S25" s="34">
+      <c r="S25" s="35">
         <v>27.11</v>
       </c>
-      <c r="T25" s="34">
+      <c r="T25" s="35">
         <v>1.41</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="35">
         <v>1.96</v>
       </c>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="34">
+      <c r="A27" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="35">
         <v>31.76</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>19.63</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>25.32</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>9.76</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="35">
         <v>10.11</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>7.91</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>6.73</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>6.2</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <v>4.25</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>3.86</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>3.91</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>4.5</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>3.97</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>3.8</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="35">
         <v>4.79</v>
       </c>
-      <c r="T27" s="34">
+      <c r="T27" s="35">
         <v>0.24</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>0.46</v>
       </c>
-      <c r="V27" s="34">
+      <c r="V27" s="35">
         <v>0.98</v>
       </c>
-      <c r="W27" s="34">
+      <c r="W27" s="35">
         <v>1.15</v>
       </c>
-      <c r="X27" s="34">
+      <c r="X27" s="35">
         <v>2.36</v>
       </c>
-      <c r="Y27" s="34">
+      <c r="Y27" s="35">
         <v>8.75</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="34">
+      <c r="A28" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="35">
         <v>19.19</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <v>15.5</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <v>11.6</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="35">
         <v>8.07</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="35">
         <v>7.17</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <v>5.74</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>5.53</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>4.83</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <v>4.45</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>4.0</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="35">
         <v>4.26</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="35">
         <v>3.53</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="Q28" s="35">
         <v>2.54</v>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="35">
         <v>2.11</v>
       </c>
-      <c r="S28" s="34">
+      <c r="S28" s="35">
         <v>1.48</v>
       </c>
-      <c r="T28" s="34">
+      <c r="T28" s="35">
         <v>1.11</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="35">
         <v>2.72</v>
       </c>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36">
+      <c r="A30" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37">
         <v>-4.65</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>-26.42</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>-3.96</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>-29.8</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>-14.94</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>-722.63</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>-108.98</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>-288.81</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <v>-228.34</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>-169.29</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>-118.24</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>-485.62</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>-82.1</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>-1053.49</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>-1255.01</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>-966.59</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="37">
         <v>-673.46</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>-611.9</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>-1115.59</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>-1042.94</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>-407.04</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="36">
+      <c r="A31" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="37">
         <v>-12.22</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>-95.38</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>-117.75</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>-218.84</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>-272.77</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>-343.4</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>-185.26</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>-266.57</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>-222.17</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>-372.79</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>-614.81</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>-729.63</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="Q31" s="37">
         <v>-808.41</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="37">
         <v>-1091.12</v>
       </c>
-      <c r="S31" s="36">
+      <c r="S31" s="37">
         <v>-1112.77</v>
       </c>
-      <c r="T31" s="36">
+      <c r="T31" s="37">
         <v>-945.36</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="37">
         <v>-601.78</v>
       </c>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35">
+      <c r="A33" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36">
         <v>1.4</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>2.23</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>1.17</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>2.8</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>24.26</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>25.17</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>17.43</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>15.14</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>18.63</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>15.52</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>15.52</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>12.87</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>0.0</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>22.34</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>0.0</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.0</v>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="36">
         <v>0.0</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="36">
         <v>0.0</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>0.0</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="36">
         <v>0.0</v>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="36">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35">
+      <c r="A34" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36">
         <v>3.98</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>7.5</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>10.13</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>16.76</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>20.89</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>18.97</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <v>16.42</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <v>15.44</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="36">
         <v>12.31</v>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="36">
         <v>12.92</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="36">
         <v>9.45</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>7.98</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="36">
         <v>6.08</v>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="36">
         <v>8.05</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="36">
         <v>0.0</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="36">
         <v>0.0</v>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="36">
         <v>0.0</v>
       </c>
-      <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
-      <c r="X34" s="35"/>
-      <c r="Y34" s="35"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35">
+      <c r="A35" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36">
         <v>1.99</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>3.19</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>1.67</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>4.0</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>34.65</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>35.96</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>24.9</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>21.63</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>26.61</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>22.17</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>22.17</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>18.39</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>0.0</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>0.0</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>0.0</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>0.0</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="36">
         <v>0.0</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>0.0</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>0.0</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="36">
         <v>0.0</v>
       </c>
-      <c r="Y35" s="35">
+      <c r="Y35" s="36">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35">
+      <c r="A36" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36">
         <v>5.69</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>10.71</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>14.47</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>23.95</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>29.85</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>27.1</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>23.46</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>22.05</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>17.59</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>12.63</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>7.95</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>4.69</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <v>0.0</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="36">
         <v>0.0</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="36">
         <v>0.0</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="36">
         <v>0.0</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="36">
         <v>0.0</v>
       </c>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>380</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="34">
+      <c r="A38" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="35">
         <v>1.07</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>0.89</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>1.2</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>0.69</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>0.85</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>0.08</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>0.08</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>0.1</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>0.07</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>0.08</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>0.08</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>0.09</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>0.1</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>0.11</v>
       </c>
-      <c r="S38" s="34">
+      <c r="S38" s="35">
         <v>0.12</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T38" s="35">
         <v>0.16</v>
       </c>
-      <c r="U38" s="34">
+      <c r="U38" s="35">
         <v>0.15</v>
       </c>
-      <c r="V38" s="34">
+      <c r="V38" s="35">
         <v>0.11</v>
       </c>
-      <c r="W38" s="34">
+      <c r="W38" s="35">
         <v>0.06</v>
       </c>
-      <c r="X38" s="34">
+      <c r="X38" s="35">
         <v>0.06</v>
       </c>
-      <c r="Y38" s="34">
+      <c r="Y38" s="35">
         <v>0.17</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="34">
+      <c r="A39" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="35">
         <v>0.98</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>0.42</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>0.26</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>0.15</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>0.11</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>0.08</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>0.08</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>0.09</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>0.09</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>0.09</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="35">
         <v>0.1</v>
       </c>
-      <c r="P39" s="34">
+      <c r="P39" s="35">
         <v>0.11</v>
       </c>
-      <c r="Q39" s="34">
+      <c r="Q39" s="35">
         <v>0.11</v>
       </c>
-      <c r="R39" s="34">
+      <c r="R39" s="35">
         <v>0.11</v>
       </c>
-      <c r="S39" s="34">
+      <c r="S39" s="35">
         <v>0.11</v>
       </c>
-      <c r="T39" s="34">
+      <c r="T39" s="35">
         <v>0.07</v>
       </c>
-      <c r="U39" s="34">
+      <c r="U39" s="35">
         <v>0.11</v>
       </c>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="31"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="34">
+      <c r="A41" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="35">
         <v>1.18</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <v>0.89</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <v>1.2</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <v>0.69</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="35">
         <v>0.85</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="35">
         <v>0.08</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="35">
         <v>0.08</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>0.1</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>0.07</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>0.08</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>0.08</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>0.09</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>0.1</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <v>0.11</v>
       </c>
-      <c r="S41" s="34">
+      <c r="S41" s="35">
         <v>0.12</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="35">
         <v>0.18</v>
       </c>
-      <c r="U41" s="34">
+      <c r="U41" s="35">
         <v>0.17</v>
       </c>
-      <c r="V41" s="34">
+      <c r="V41" s="35">
         <v>0.26</v>
       </c>
-      <c r="W41" s="34">
+      <c r="W41" s="35">
         <v>0.12</v>
       </c>
-      <c r="X41" s="34">
+      <c r="X41" s="35">
         <v>0.15</v>
       </c>
-      <c r="Y41" s="34">
+      <c r="Y41" s="35">
         <v>0.7</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="34">
+      <c r="A42" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="35">
         <v>1.01</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <v>0.42</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <v>0.26</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <v>0.15</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>0.11</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="35">
         <v>0.08</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="35">
         <v>0.08</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="35">
         <v>0.09</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>0.09</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>0.09</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="35">
         <v>0.1</v>
       </c>
-      <c r="P42" s="34">
+      <c r="P42" s="35">
         <v>0.11</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <v>0.11</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R42" s="35">
         <v>0.12</v>
       </c>
-      <c r="S42" s="34">
+      <c r="S42" s="35">
         <v>0.13</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T42" s="35">
         <v>0.16</v>
       </c>
-      <c r="U42" s="34">
+      <c r="U42" s="35">
         <v>0.31</v>
       </c>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
-      <c r="Y42" s="31"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="34">
+      <c r="A44" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="35">
         <v>8.61</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>7.22</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>10.23</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>3.78</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>4.17</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>0.4</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>0.38</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>0.39</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>0.31</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.31</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>0.34</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>0.36</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>0.35</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>0.31</v>
       </c>
-      <c r="S44" s="34">
+      <c r="S44" s="35">
         <v>2.87</v>
       </c>
-      <c r="T44" s="34">
+      <c r="T44" s="35">
         <v>0.61</v>
       </c>
-      <c r="U44" s="34">
+      <c r="U44" s="35">
         <v>1.36</v>
       </c>
-      <c r="V44" s="34">
+      <c r="V44" s="35">
         <v>1.49</v>
       </c>
-      <c r="W44" s="34">
+      <c r="W44" s="35">
         <v>0.82</v>
       </c>
-      <c r="X44" s="34">
+      <c r="X44" s="35">
         <v>1.2</v>
       </c>
-      <c r="Y44" s="34">
+      <c r="Y44" s="35">
         <v>5.31</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="34">
+      <c r="A45" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="35">
         <v>6.99</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>2.4</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>1.36</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>0.7</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>0.5</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>0.36</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>0.35</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>0.34</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>0.33</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>0.33</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="35">
         <v>0.43</v>
       </c>
-      <c r="P45" s="34">
+      <c r="P45" s="35">
         <v>0.45</v>
       </c>
-      <c r="Q45" s="34">
+      <c r="Q45" s="35">
         <v>0.51</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R45" s="35">
         <v>0.68</v>
       </c>
-      <c r="S45" s="34">
+      <c r="S45" s="35">
         <v>1.74</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="35">
         <v>1.1</v>
       </c>
-      <c r="U45" s="34">
+      <c r="U45" s="35">
         <v>2.28</v>
       </c>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
-      <c r="X45" s="31"/>
-      <c r="Y45" s="31"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="34">
+      <c r="A47" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="35">
         <v>2.12</v>
       </c>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="31"/>
-      <c r="Y47" s="31"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
+      <c r="A48" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="34">
+      <c r="A49" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="35">
         <v>5.67</v>
       </c>
-      <c r="F49" s="31"/>
-      <c r="G49" s="34">
+      <c r="F49" s="32"/>
+      <c r="G49" s="35">
         <v>3.23</v>
       </c>
-      <c r="H49" s="34">
+      <c r="H49" s="35">
         <v>3.28</v>
       </c>
-      <c r="I49" s="34">
+      <c r="I49" s="35">
         <v>4.34</v>
       </c>
-      <c r="J49" s="34">
+      <c r="J49" s="35">
         <v>0.35</v>
       </c>
-      <c r="K49" s="34">
+      <c r="K49" s="35">
         <v>0.32</v>
       </c>
-      <c r="L49" s="34">
+      <c r="L49" s="35">
         <v>5.19</v>
       </c>
-      <c r="M49" s="34">
+      <c r="M49" s="35">
         <v>0.55</v>
       </c>
-      <c r="N49" s="34">
+      <c r="N49" s="35">
         <v>1.5</v>
       </c>
-      <c r="O49" s="31"/>
-      <c r="P49" s="34">
+      <c r="O49" s="32"/>
+      <c r="P49" s="35">
         <v>0.45</v>
       </c>
-      <c r="Q49" s="34">
+      <c r="Q49" s="35">
         <v>0.68</v>
       </c>
-      <c r="R49" s="31"/>
-      <c r="S49" s="34">
+      <c r="R49" s="32"/>
+      <c r="S49" s="35">
         <v>0.65</v>
       </c>
-      <c r="T49" s="31"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
-      <c r="X49" s="31"/>
-      <c r="Y49" s="31"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="34">
+      <c r="A50" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="35">
         <v>5.2</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <v>2.02</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <v>1.08</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <v>0.82</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="35">
         <v>0.65</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>0.54</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>0.83</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>1.08</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>0.81</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>1.93</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>1.37</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>1.27</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="35">
         <v>21.7</v>
       </c>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="31"/>
-      <c r="Y50" s="31"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
+      <c r="Y50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="29"/>
-      <c r="T51" s="29"/>
-      <c r="U51" s="29"/>
-      <c r="V51" s="29"/>
-      <c r="W51" s="29"/>
-      <c r="X51" s="29"/>
-      <c r="Y51" s="29"/>
+      <c r="A51" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30"/>
+      <c r="Y51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="34">
+      <c r="A52" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="35">
         <v>5.8</v>
       </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="34">
+      <c r="F52" s="32"/>
+      <c r="G52" s="35">
         <v>3.23</v>
       </c>
-      <c r="H52" s="34">
+      <c r="H52" s="35">
         <v>3.28</v>
       </c>
-      <c r="I52" s="34">
+      <c r="I52" s="35">
         <v>4.34</v>
       </c>
-      <c r="J52" s="34">
+      <c r="J52" s="35">
         <v>0.35</v>
       </c>
-      <c r="K52" s="34">
+      <c r="K52" s="35">
         <v>0.32</v>
       </c>
-      <c r="L52" s="34">
+      <c r="L52" s="35">
         <v>5.3</v>
       </c>
-      <c r="M52" s="34">
+      <c r="M52" s="35">
         <v>0.56</v>
       </c>
-      <c r="N52" s="34">
+      <c r="N52" s="35">
         <v>1.52</v>
       </c>
-      <c r="O52" s="31"/>
-      <c r="P52" s="34">
+      <c r="O52" s="32"/>
+      <c r="P52" s="35">
         <v>0.45</v>
       </c>
-      <c r="Q52" s="34">
+      <c r="Q52" s="35">
         <v>0.68</v>
       </c>
-      <c r="R52" s="31"/>
-      <c r="S52" s="34">
+      <c r="R52" s="32"/>
+      <c r="S52" s="35">
         <v>0.65</v>
       </c>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
-      <c r="W52" s="31"/>
-      <c r="X52" s="31"/>
-      <c r="Y52" s="31"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="34">
+      <c r="A53" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="35">
         <v>5.23</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <v>2.02</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <v>1.08</v>
       </c>
-      <c r="H53" s="34">
+      <c r="H53" s="35">
         <v>0.82</v>
       </c>
-      <c r="I53" s="34">
+      <c r="I53" s="35">
         <v>0.65</v>
       </c>
-      <c r="J53" s="34">
+      <c r="J53" s="35">
         <v>0.54</v>
       </c>
-      <c r="K53" s="34">
+      <c r="K53" s="35">
         <v>0.84</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>1.09</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>0.81</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="35">
         <v>1.95</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="35">
         <v>1.38</v>
       </c>
-      <c r="P53" s="34">
+      <c r="P53" s="35">
         <v>1.32</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <v>4.11</v>
       </c>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
-      <c r="Y53" s="31"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
+      <c r="X53" s="32"/>
+      <c r="Y53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
-      <c r="Q54" s="29"/>
-      <c r="R54" s="29"/>
-      <c r="S54" s="29"/>
-      <c r="T54" s="29"/>
-      <c r="U54" s="29"/>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
-      <c r="X54" s="29"/>
-      <c r="Y54" s="29"/>
+      <c r="A54" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="30"/>
+      <c r="Y54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="32">
+      <c r="A55" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="33">
         <v>129.13</v>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="35">
         <v>40.81</v>
       </c>
-      <c r="H55" s="34">
+      <c r="H55" s="35">
         <v>5.69</v>
       </c>
-      <c r="I55" s="34">
+      <c r="I55" s="35">
         <v>8.18</v>
       </c>
-      <c r="J55" s="34">
+      <c r="J55" s="35">
         <v>0.72</v>
       </c>
-      <c r="K55" s="34">
+      <c r="K55" s="35">
         <v>0.65</v>
       </c>
-      <c r="L55" s="34">
+      <c r="L55" s="35">
         <v>0.92</v>
       </c>
-      <c r="M55" s="34">
+      <c r="M55" s="35">
         <v>1.11</v>
       </c>
-      <c r="N55" s="34">
+      <c r="N55" s="35">
         <v>1.34</v>
       </c>
-      <c r="O55" s="34">
+      <c r="O55" s="35">
         <v>1.35</v>
       </c>
-      <c r="P55" s="34">
+      <c r="P55" s="35">
         <v>2.48</v>
       </c>
-      <c r="Q55" s="34">
+      <c r="Q55" s="35">
         <v>0.95</v>
       </c>
-      <c r="R55" s="34">
+      <c r="R55" s="35">
         <v>0.62</v>
       </c>
-      <c r="S55" s="34">
+      <c r="S55" s="35">
         <v>1.35</v>
       </c>
-      <c r="T55" s="31"/>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
-      <c r="W55" s="31"/>
-      <c r="X55" s="31"/>
-      <c r="Y55" s="31"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="34">
+      <c r="A56" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="35">
         <v>0.98</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <v>0.42</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="35">
         <v>0.26</v>
       </c>
-      <c r="H56" s="34">
+      <c r="H56" s="35">
         <v>0.15</v>
       </c>
-      <c r="I56" s="34">
+      <c r="I56" s="35">
         <v>0.11</v>
       </c>
-      <c r="J56" s="34">
+      <c r="J56" s="35">
         <v>0.08</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="35">
         <v>0.08</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>0.09</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="35">
         <v>0.09</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="35">
         <v>0.09</v>
       </c>
-      <c r="O56" s="34">
+      <c r="O56" s="35">
         <v>0.1</v>
       </c>
-      <c r="P56" s="34">
+      <c r="P56" s="35">
         <v>0.11</v>
       </c>
-      <c r="Q56" s="34">
+      <c r="Q56" s="35">
         <v>0.11</v>
       </c>
-      <c r="R56" s="34">
+      <c r="R56" s="35">
         <v>0.11</v>
       </c>
-      <c r="S56" s="34">
+      <c r="S56" s="35">
         <v>0.11</v>
       </c>
-      <c r="T56" s="34">
+      <c r="T56" s="35">
         <v>0.07</v>
       </c>
-      <c r="U56" s="34">
+      <c r="U56" s="35">
         <v>0.11</v>
       </c>
-      <c r="V56" s="31"/>
-      <c r="W56" s="31"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="31"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
+      <c r="X56" s="32"/>
+      <c r="Y56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="29"/>
-      <c r="T57" s="29"/>
-      <c r="U57" s="29"/>
-      <c r="V57" s="29"/>
-      <c r="W57" s="29"/>
-      <c r="X57" s="29"/>
-      <c r="Y57" s="29"/>
+      <c r="A57" s="29" t="s">
+        <v>400</v>
+      </c>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="30"/>
+      <c r="S57" s="30"/>
+      <c r="T57" s="30"/>
+      <c r="U57" s="30"/>
+      <c r="V57" s="30"/>
+      <c r="W57" s="30"/>
+      <c r="X57" s="30"/>
+      <c r="Y57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31">
+      <c r="A58" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32">
         <v>0.0</v>
       </c>
-      <c r="F58" s="31"/>
-      <c r="G58" s="34">
+      <c r="F58" s="32"/>
+      <c r="G58" s="35">
         <v>0.02</v>
       </c>
-      <c r="H58" s="34">
+      <c r="H58" s="35">
         <v>0.11</v>
       </c>
-      <c r="I58" s="33">
+      <c r="I58" s="34">
         <v>-0.05</v>
       </c>
-      <c r="J58" s="34">
+      <c r="J58" s="35">
         <v>0.02</v>
       </c>
-      <c r="K58" s="31">
+      <c r="K58" s="32">
         <v>0.0</v>
       </c>
-      <c r="L58" s="33">
+      <c r="L58" s="34">
         <v>-0.06</v>
       </c>
-      <c r="M58" s="31">
+      <c r="M58" s="32">
         <v>0.0</v>
       </c>
-      <c r="N58" s="31">
+      <c r="N58" s="32">
         <v>0.0</v>
       </c>
-      <c r="O58" s="31"/>
-      <c r="P58" s="34">
+      <c r="O58" s="32"/>
+      <c r="P58" s="35">
         <v>0.01</v>
       </c>
-      <c r="Q58" s="31">
+      <c r="Q58" s="32">
         <v>0.0</v>
       </c>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31">
+      <c r="R58" s="32"/>
+      <c r="S58" s="32">
         <v>0.0</v>
       </c>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
-      <c r="X58" s="31"/>
-      <c r="Y58" s="31"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
+      <c r="X58" s="32"/>
+      <c r="Y58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="33">
+      <c r="A59" s="31" t="s">
+        <v>402</v>
+      </c>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="34">
         <v>-0.21</v>
       </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="34">
+      <c r="F59" s="32"/>
+      <c r="G59" s="35">
         <v>0.02</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>-0.05</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>-0.14</v>
       </c>
-      <c r="J59" s="31"/>
-      <c r="K59" s="34">
+      <c r="J59" s="32"/>
+      <c r="K59" s="35">
         <v>0.07</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>-0.04</v>
       </c>
-      <c r="M59" s="31"/>
-      <c r="N59" s="33">
+      <c r="M59" s="32"/>
+      <c r="N59" s="34">
         <v>-0.1</v>
       </c>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="32"/>
+      <c r="X59" s="32"/>
+      <c r="Y59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
-      <c r="R60" s="29"/>
-      <c r="S60" s="29"/>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
-      <c r="W60" s="29"/>
-      <c r="X60" s="29"/>
-      <c r="Y60" s="29"/>
+      <c r="A60" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
+      <c r="X60" s="30"/>
+      <c r="Y60" s="30"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B61" s="34">
+      <c r="A61" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="B61" s="35">
         <v>12.41</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C61" s="35">
         <v>11.84</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="35">
         <v>13.48</v>
       </c>
-      <c r="E61" s="34">
+      <c r="E61" s="35">
         <v>32.25</v>
       </c>
-      <c r="F61" s="34">
+      <c r="F61" s="35">
         <v>20.15</v>
       </c>
-      <c r="G61" s="34">
+      <c r="G61" s="35">
         <v>18.28</v>
       </c>
-      <c r="H61" s="34">
+      <c r="H61" s="35">
         <v>14.83</v>
       </c>
-      <c r="I61" s="34">
+      <c r="I61" s="35">
         <v>13.92</v>
       </c>
-      <c r="J61" s="34">
+      <c r="J61" s="35">
         <v>11.97</v>
       </c>
-      <c r="K61" s="34">
+      <c r="K61" s="35">
         <v>10.89</v>
       </c>
-      <c r="L61" s="34">
+      <c r="L61" s="35">
         <v>11.34</v>
       </c>
-      <c r="M61" s="34">
+      <c r="M61" s="35">
         <v>10.7</v>
       </c>
-      <c r="N61" s="34">
+      <c r="N61" s="35">
         <v>9.98</v>
       </c>
-      <c r="O61" s="34">
+      <c r="O61" s="35">
         <v>10.28</v>
       </c>
-      <c r="P61" s="34">
+      <c r="P61" s="35">
         <v>8.34</v>
       </c>
-      <c r="Q61" s="34">
+      <c r="Q61" s="35">
         <v>6.5</v>
       </c>
-      <c r="R61" s="34">
+      <c r="R61" s="35">
         <v>8.11</v>
       </c>
-      <c r="S61" s="34">
+      <c r="S61" s="35">
         <v>38.5</v>
       </c>
-      <c r="T61" s="33">
+      <c r="T61" s="34">
         <v>-3.01</v>
       </c>
-      <c r="U61" s="33">
+      <c r="U61" s="34">
         <v>-6.74</v>
       </c>
-      <c r="V61" s="33">
+      <c r="V61" s="34">
         <v>-1.86</v>
       </c>
-      <c r="W61" s="33">
+      <c r="W61" s="34">
         <v>-6.29</v>
       </c>
-      <c r="X61" s="33">
+      <c r="X61" s="34">
         <v>-3.11</v>
       </c>
-      <c r="Y61" s="34">
+      <c r="Y61" s="35">
         <v>0.15</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="31" t="s">
+        <v>405</v>
+      </c>
+      <c r="B62" s="35">
         <v>16.44</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>17.68</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>19.86</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>23.43</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>15.98</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>14.33</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>12.87</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>11.97</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>11.04</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>10.67</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>10.22</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>9.28</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>8.75</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>9.25</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>8.86</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>9.11</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>11.67</v>
       </c>
-      <c r="S62" s="34">
+      <c r="S62" s="35">
         <v>34.87</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>-4.1</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>-3.57</v>
       </c>
-      <c r="V62" s="31"/>
-      <c r="W62" s="31"/>
-      <c r="X62" s="31"/>
-      <c r="Y62" s="31"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="32"/>
+      <c r="X62" s="32"/>
+      <c r="Y62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-      <c r="T63" s="29"/>
-      <c r="U63" s="29"/>
-      <c r="V63" s="29"/>
-      <c r="W63" s="29"/>
-      <c r="X63" s="29"/>
-      <c r="Y63" s="29"/>
+      <c r="A63" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="30"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="30"/>
+      <c r="S63" s="30"/>
+      <c r="T63" s="30"/>
+      <c r="U63" s="30"/>
+      <c r="V63" s="30"/>
+      <c r="W63" s="30"/>
+      <c r="X63" s="30"/>
+      <c r="Y63" s="30"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>406</v>
-      </c>
-      <c r="B64" s="34">
+      <c r="A64" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="B64" s="35">
         <v>20.61</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="35">
         <v>18.43</v>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="35">
         <v>21.84</v>
       </c>
-      <c r="E64" s="34">
+      <c r="E64" s="35">
         <v>50.6</v>
       </c>
-      <c r="F64" s="34">
+      <c r="F64" s="35">
         <v>28.6</v>
       </c>
-      <c r="G64" s="34">
+      <c r="G64" s="35">
         <v>26.5</v>
       </c>
-      <c r="H64" s="34">
+      <c r="H64" s="35">
         <v>20.62</v>
       </c>
-      <c r="I64" s="34">
+      <c r="I64" s="35">
         <v>18.82</v>
       </c>
-      <c r="J64" s="34">
+      <c r="J64" s="35">
         <v>16.32</v>
       </c>
-      <c r="K64" s="34">
+      <c r="K64" s="35">
         <v>15.46</v>
       </c>
-      <c r="L64" s="34">
+      <c r="L64" s="35">
         <v>15.48</v>
       </c>
-      <c r="M64" s="34">
+      <c r="M64" s="35">
         <v>15.33</v>
       </c>
-      <c r="N64" s="34">
+      <c r="N64" s="35">
         <v>14.06</v>
       </c>
-      <c r="O64" s="34">
+      <c r="O64" s="35">
         <v>14.98</v>
       </c>
-      <c r="P64" s="34">
+      <c r="P64" s="35">
         <v>12.19</v>
       </c>
-      <c r="Q64" s="34">
+      <c r="Q64" s="35">
         <v>8.97</v>
       </c>
-      <c r="R64" s="34">
+      <c r="R64" s="35">
         <v>12.59</v>
       </c>
-      <c r="S64" s="34">
+      <c r="S64" s="35">
         <v>89.62</v>
       </c>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="31"/>
-      <c r="Y64" s="31"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="32"/>
+      <c r="Y64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="B65" s="35">
         <v>26.15</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>27.61</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>30.69</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>34.43</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <v>22.3</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="35">
         <v>19.98</v>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="35">
         <v>17.71</v>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="35">
         <v>16.53</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>15.41</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>15.09</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>14.52</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>13.25</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>12.64</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>13.63</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>13.26</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="Q65" s="35">
         <v>14.06</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>21.21</v>
       </c>
-      <c r="S65" s="34">
+      <c r="S65" s="35">
         <v>20.63</v>
       </c>
-      <c r="T65" s="31"/>
-      <c r="U65" s="31"/>
-      <c r="V65" s="31"/>
-      <c r="W65" s="31"/>
-      <c r="X65" s="31"/>
-      <c r="Y65" s="31"/>
+      <c r="T65" s="32"/>
+      <c r="U65" s="32"/>
+      <c r="V65" s="32"/>
+      <c r="W65" s="32"/>
+      <c r="X65" s="32"/>
+      <c r="Y65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
-      <c r="O66" s="29"/>
-      <c r="P66" s="29"/>
-      <c r="Q66" s="29"/>
-      <c r="R66" s="29"/>
-      <c r="S66" s="29"/>
-      <c r="T66" s="29"/>
-      <c r="U66" s="29"/>
-      <c r="V66" s="29"/>
-      <c r="W66" s="29"/>
-      <c r="X66" s="29"/>
-      <c r="Y66" s="29"/>
+      <c r="A66" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="30"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
+      <c r="R66" s="30"/>
+      <c r="S66" s="30"/>
+      <c r="T66" s="30"/>
+      <c r="U66" s="30"/>
+      <c r="V66" s="30"/>
+      <c r="W66" s="30"/>
+      <c r="X66" s="30"/>
+      <c r="Y66" s="30"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>409</v>
-      </c>
-      <c r="B67" s="34">
+      <c r="A67" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="B67" s="35">
         <v>49.83</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="35">
         <v>69.98</v>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="35">
         <v>27.12</v>
       </c>
-      <c r="E67" s="34">
+      <c r="E67" s="35">
         <v>76.03</v>
       </c>
-      <c r="F67" s="34">
+      <c r="F67" s="35">
         <v>48.69</v>
       </c>
-      <c r="G67" s="34">
+      <c r="G67" s="35">
         <v>37.62</v>
       </c>
-      <c r="H67" s="34">
+      <c r="H67" s="35">
         <v>31.94</v>
       </c>
-      <c r="I67" s="34">
+      <c r="I67" s="35">
         <v>28.48</v>
       </c>
-      <c r="J67" s="34">
+      <c r="J67" s="35">
         <v>21.56</v>
       </c>
-      <c r="K67" s="34">
+      <c r="K67" s="35">
         <v>20.17</v>
       </c>
-      <c r="L67" s="34">
+      <c r="L67" s="35">
         <v>62.34</v>
       </c>
-      <c r="M67" s="34">
+      <c r="M67" s="35">
         <v>23.69</v>
       </c>
-      <c r="N67" s="34">
+      <c r="N67" s="35">
         <v>29.49</v>
       </c>
-      <c r="O67" s="34">
+      <c r="O67" s="35">
         <v>88.09</v>
       </c>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="34">
+      <c r="P67" s="32"/>
+      <c r="Q67" s="35">
         <v>29.17</v>
       </c>
-      <c r="R67" s="31"/>
-      <c r="S67" s="34">
+      <c r="R67" s="32"/>
+      <c r="S67" s="35">
         <v>39.98</v>
       </c>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
-      <c r="X67" s="31"/>
-      <c r="Y67" s="31"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
+      <c r="X67" s="32"/>
+      <c r="Y67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="B68" s="35">
         <v>48.82</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>47.59</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>42.68</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <v>52.45</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <v>33.37</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>28.56</v>
       </c>
-      <c r="H68" s="34">
+      <c r="H68" s="35">
         <v>28.32</v>
       </c>
-      <c r="I68" s="34">
+      <c r="I68" s="35">
         <v>26.53</v>
       </c>
-      <c r="J68" s="34">
+      <c r="J68" s="35">
         <v>26.29</v>
       </c>
-      <c r="K68" s="34">
+      <c r="K68" s="35">
         <v>32.14</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>54.02</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>47.13</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>131.15</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>712.97</v>
       </c>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="32">
+      <c r="P68" s="32"/>
+      <c r="Q68" s="33">
         <v>174.35</v>
       </c>
-      <c r="R68" s="31"/>
-      <c r="S68" s="32">
+      <c r="R68" s="32"/>
+      <c r="S68" s="33">
         <v>151.86</v>
       </c>
-      <c r="T68" s="31"/>
-      <c r="U68" s="31"/>
-      <c r="V68" s="31"/>
-      <c r="W68" s="31"/>
-      <c r="X68" s="31"/>
-      <c r="Y68" s="31"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
+      <c r="X68" s="32"/>
+      <c r="Y68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>411</v>
-      </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29"/>
-      <c r="P69" s="29"/>
-      <c r="Q69" s="29"/>
-      <c r="R69" s="29"/>
-      <c r="S69" s="29"/>
-      <c r="T69" s="29"/>
-      <c r="U69" s="29"/>
-      <c r="V69" s="29"/>
-      <c r="W69" s="29"/>
-      <c r="X69" s="29"/>
-      <c r="Y69" s="29"/>
+      <c r="A69" s="29" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="30"/>
+      <c r="S69" s="30"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="30"/>
+      <c r="Y69" s="30"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="34">
+      <c r="A70" s="31" t="s">
+        <v>413</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="35">
         <v>48.55</v>
       </c>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
-      <c r="W70" s="31"/>
-      <c r="X70" s="31"/>
-      <c r="Y70" s="31"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
+      <c r="W70" s="32"/>
+      <c r="X70" s="32"/>
+      <c r="Y70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-      <c r="N71" s="31"/>
-      <c r="O71" s="31"/>
-      <c r="P71" s="31"/>
-      <c r="Q71" s="31"/>
-      <c r="R71" s="31"/>
-      <c r="S71" s="32">
+      <c r="A71" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
+      <c r="S71" s="33">
         <v>893.57</v>
       </c>
-      <c r="T71" s="31"/>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="31"/>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="31"/>
+      <c r="T71" s="32"/>
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="32"/>
+      <c r="X71" s="32"/>
+      <c r="Y71" s="32"/>
     </row>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
